--- a/docs/项目开发总任务分配.xlsx
+++ b/docs/项目开发总任务分配.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24750" windowHeight="10740"/>
+    <workbookView windowWidth="11920" windowHeight="10140"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="73">
   <si>
     <t>小组</t>
   </si>
@@ -59,6 +59,9 @@
   </si>
   <si>
     <t>输入框，文件选择</t>
+  </si>
+  <si>
+    <t>林浩</t>
   </si>
   <si>
     <t>项目信息配置</t>
@@ -144,6 +147,9 @@
     <t>实现的优先级低一点，先实现可以正常向网页输出报告。</t>
   </si>
   <si>
+    <t>廖旭飞</t>
+  </si>
+  <si>
     <t>评分等级判定</t>
   </si>
   <si>
@@ -177,7 +183,17 @@
     <t>原项目包含：文件操作工具、Git操作工具、语言类型检测。但本项目只实现files.go的功能。</t>
   </si>
   <si>
+    <t>梁智鹭</t>
+  </si>
+  <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>Parser模块</t>
     </r>
     <r>
@@ -214,6 +230,9 @@
   </si>
   <si>
     <t>cyclomatic_complexity.go</t>
+  </si>
+  <si>
+    <t>马锟阳，李嘉耀</t>
   </si>
   <si>
     <t>函数长度分析</t>
@@ -997,7 +1016,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1027,12 +1046,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1419,21 +1432,23 @@
       <c r="G2" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="H2" s="5"/>
+      <c r="H2" s="5" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="3" ht="35" customHeight="1" spans="1:8">
       <c r="A3" s="3"/>
       <c r="B3" s="4"/>
       <c r="C3" s="4"/>
       <c r="D3" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E3" s="3"/>
       <c r="F3" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H3" s="6"/>
     </row>
@@ -1444,10 +1459,10 @@
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
       <c r="F4" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G4" s="3" t="s">
         <v>13</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>12</v>
       </c>
       <c r="H4" s="6"/>
     </row>
@@ -1458,7 +1473,7 @@
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
       <c r="F5" s="3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G5" s="3"/>
       <c r="H5" s="7"/>
@@ -1466,20 +1481,22 @@
     <row r="6" ht="35" customHeight="1" spans="1:8">
       <c r="A6" s="3"/>
       <c r="B6" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C6" s="4"/>
       <c r="D6" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E6" s="4"/>
       <c r="F6" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="H6" s="5"/>
+        <v>19</v>
+      </c>
+      <c r="H6" s="5" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="7" ht="35" customHeight="1" spans="1:8">
       <c r="A7" s="3"/>
@@ -1488,10 +1505,10 @@
       <c r="D7" s="4"/>
       <c r="E7" s="4"/>
       <c r="F7" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H7" s="6"/>
     </row>
@@ -1500,11 +1517,11 @@
       <c r="B8" s="4"/>
       <c r="C8" s="4"/>
       <c r="D8" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E8" s="4"/>
       <c r="F8" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G8" s="3"/>
       <c r="H8" s="7"/>
@@ -1512,15 +1529,15 @@
     <row r="9" ht="35" customHeight="1" spans="1:8">
       <c r="A9" s="3"/>
       <c r="B9" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C9" s="4"/>
       <c r="D9" s="4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E9" s="4"/>
       <c r="F9" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G9" s="4"/>
       <c r="H9" s="5"/>
@@ -1530,14 +1547,14 @@
       <c r="B10" s="4"/>
       <c r="C10" s="4"/>
       <c r="D10" s="8" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E10" s="8"/>
       <c r="F10" s="8" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H10" s="6"/>
     </row>
@@ -1546,248 +1563,258 @@
       <c r="B11" s="4"/>
       <c r="C11" s="4"/>
       <c r="D11" s="8" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E11" s="8"/>
       <c r="F11" s="8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G11" s="9" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H11" s="7"/>
     </row>
     <row r="12" ht="35" customHeight="1" spans="1:8">
       <c r="A12" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="B12" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="C12" s="10"/>
-      <c r="D12" s="11" t="s">
+      <c r="B12" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="E12" s="11"/>
-      <c r="F12" s="10" t="s">
+      <c r="C12" s="9"/>
+      <c r="D12" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="G12" s="10" t="s">
+      <c r="E12" s="8"/>
+      <c r="F12" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="H12" s="5"/>
+      <c r="G12" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="H12" s="5" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="13" ht="35" customHeight="1" spans="1:8">
       <c r="A13" s="6"/>
-      <c r="B13" s="10"/>
-      <c r="C13" s="10"/>
-      <c r="D13" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="E13" s="11"/>
-      <c r="F13" s="10"/>
-      <c r="G13" s="11" t="s">
-        <v>38</v>
+      <c r="B13" s="9"/>
+      <c r="C13" s="9"/>
+      <c r="D13" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="E13" s="8"/>
+      <c r="F13" s="9"/>
+      <c r="G13" s="8" t="s">
+        <v>40</v>
       </c>
       <c r="H13" s="6"/>
     </row>
     <row r="14" ht="35" customHeight="1" spans="1:8">
       <c r="A14" s="6"/>
-      <c r="B14" s="10"/>
-      <c r="C14" s="10"/>
-      <c r="D14" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="E14" s="11"/>
-      <c r="F14" s="10"/>
-      <c r="G14" s="11"/>
+      <c r="B14" s="9"/>
+      <c r="C14" s="9"/>
+      <c r="D14" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="E14" s="8"/>
+      <c r="F14" s="9"/>
+      <c r="G14" s="8"/>
       <c r="H14" s="7"/>
     </row>
     <row r="15" ht="35" customHeight="1" spans="1:8">
       <c r="A15" s="6"/>
-      <c r="B15" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="C15" s="11"/>
-      <c r="D15" s="11" t="s">
-        <v>41</v>
-      </c>
-      <c r="E15" s="11"/>
-      <c r="F15" s="11" t="s">
+      <c r="B15" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="G15" s="11"/>
-      <c r="H15" s="5"/>
+      <c r="C15" s="8"/>
+      <c r="D15" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="E15" s="8"/>
+      <c r="F15" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="G15" s="8"/>
+      <c r="H15" s="5" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="16" ht="35" customHeight="1" spans="1:8">
       <c r="A16" s="6"/>
-      <c r="B16" s="11"/>
-      <c r="C16" s="11"/>
-      <c r="D16" s="11" t="s">
-        <v>43</v>
-      </c>
-      <c r="E16" s="11"/>
-      <c r="F16" s="11"/>
-      <c r="G16" s="11"/>
+      <c r="B16" s="8"/>
+      <c r="C16" s="8"/>
+      <c r="D16" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="E16" s="8"/>
+      <c r="F16" s="8"/>
+      <c r="G16" s="8"/>
       <c r="H16" s="6"/>
     </row>
     <row r="17" ht="35" customHeight="1" spans="1:8">
       <c r="A17" s="6"/>
-      <c r="B17" s="11"/>
-      <c r="C17" s="11"/>
-      <c r="D17" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="E17" s="11"/>
-      <c r="F17" s="11"/>
-      <c r="G17" s="11"/>
+      <c r="B17" s="8"/>
+      <c r="C17" s="8"/>
+      <c r="D17" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="E17" s="8"/>
+      <c r="F17" s="8"/>
+      <c r="G17" s="8"/>
       <c r="H17" s="7"/>
     </row>
     <row r="18" ht="35" customHeight="1" spans="1:8">
       <c r="A18" s="6"/>
-      <c r="B18" s="11" t="s">
-        <v>45</v>
-      </c>
-      <c r="C18" s="11"/>
-      <c r="D18" s="11" t="s">
-        <v>46</v>
-      </c>
-      <c r="E18" s="11"/>
-      <c r="F18" s="12"/>
-      <c r="G18" s="10" t="s">
+      <c r="B18" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="H18" s="12"/>
+      <c r="C18" s="8"/>
+      <c r="D18" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="E18" s="8"/>
+      <c r="F18" s="10"/>
+      <c r="G18" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="H18" s="8" t="s">
+        <v>50</v>
+      </c>
     </row>
     <row r="19" ht="35" customHeight="1" spans="1:8">
       <c r="A19" s="6"/>
-      <c r="B19" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="C19" s="11"/>
-      <c r="D19" s="11" t="s">
-        <v>49</v>
-      </c>
-      <c r="E19" s="11"/>
-      <c r="F19" s="11"/>
-      <c r="G19" s="11" t="s">
+      <c r="B19" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="C19" s="8"/>
+      <c r="D19" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="E19" s="8"/>
+      <c r="F19" s="8"/>
+      <c r="G19" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="H19" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="H19" s="5"/>
     </row>
     <row r="20" ht="35" customHeight="1" spans="1:8">
       <c r="A20" s="6"/>
-      <c r="B20" s="11"/>
-      <c r="C20" s="11"/>
-      <c r="D20" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="E20" s="11"/>
-      <c r="F20" s="11"/>
-      <c r="G20" s="11" t="s">
-        <v>52</v>
+      <c r="B20" s="8"/>
+      <c r="C20" s="8"/>
+      <c r="D20" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="E20" s="8"/>
+      <c r="F20" s="8"/>
+      <c r="G20" s="8" t="s">
+        <v>55</v>
       </c>
       <c r="H20" s="7"/>
     </row>
     <row r="21" ht="35" customHeight="1" spans="1:8">
       <c r="A21" s="6"/>
-      <c r="B21" s="13" t="s">
-        <v>53</v>
-      </c>
-      <c r="C21" s="14"/>
-      <c r="D21" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="E21" s="11"/>
-      <c r="F21" s="15" t="s">
-        <v>55</v>
-      </c>
-      <c r="G21" s="11" t="s">
+      <c r="B21" s="11" t="s">
         <v>56</v>
       </c>
-      <c r="H21" s="5"/>
+      <c r="C21" s="12"/>
+      <c r="D21" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="E21" s="8"/>
+      <c r="F21" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="G21" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="H21" s="5" t="s">
+        <v>60</v>
+      </c>
     </row>
     <row r="22" ht="35" customHeight="1" spans="1:8">
       <c r="A22" s="6"/>
-      <c r="B22" s="16"/>
-      <c r="C22" s="17"/>
-      <c r="D22" s="11" t="s">
-        <v>57</v>
-      </c>
-      <c r="E22" s="11"/>
+      <c r="B22" s="14"/>
+      <c r="C22" s="15"/>
+      <c r="D22" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="E22" s="8"/>
       <c r="F22" s="6"/>
-      <c r="G22" s="11" t="s">
-        <v>58</v>
+      <c r="G22" s="8" t="s">
+        <v>62</v>
       </c>
       <c r="H22" s="6"/>
     </row>
     <row r="23" ht="35" customHeight="1" spans="1:8">
       <c r="A23" s="6"/>
-      <c r="B23" s="16"/>
-      <c r="C23" s="17"/>
-      <c r="D23" s="11" t="s">
-        <v>59</v>
-      </c>
-      <c r="E23" s="11"/>
+      <c r="B23" s="14"/>
+      <c r="C23" s="15"/>
+      <c r="D23" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="E23" s="8"/>
       <c r="F23" s="6"/>
-      <c r="G23" s="11" t="s">
-        <v>60</v>
+      <c r="G23" s="8" t="s">
+        <v>64</v>
       </c>
       <c r="H23" s="6"/>
     </row>
     <row r="24" ht="35" customHeight="1" spans="1:8">
       <c r="A24" s="6"/>
-      <c r="B24" s="16"/>
-      <c r="C24" s="17"/>
-      <c r="D24" s="11" t="s">
-        <v>61</v>
-      </c>
-      <c r="E24" s="11"/>
+      <c r="B24" s="14"/>
+      <c r="C24" s="15"/>
+      <c r="D24" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="E24" s="8"/>
       <c r="F24" s="6"/>
-      <c r="G24" s="11" t="s">
-        <v>62</v>
+      <c r="G24" s="8" t="s">
+        <v>66</v>
       </c>
       <c r="H24" s="6"/>
     </row>
     <row r="25" ht="35" customHeight="1" spans="1:8">
       <c r="A25" s="6"/>
-      <c r="B25" s="16"/>
-      <c r="C25" s="17"/>
-      <c r="D25" s="11" t="s">
-        <v>63</v>
-      </c>
-      <c r="E25" s="11"/>
+      <c r="B25" s="14"/>
+      <c r="C25" s="15"/>
+      <c r="D25" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="E25" s="8"/>
       <c r="F25" s="6"/>
-      <c r="G25" s="11" t="s">
-        <v>64</v>
+      <c r="G25" s="8" t="s">
+        <v>68</v>
       </c>
       <c r="H25" s="6"/>
     </row>
     <row r="26" ht="35" customHeight="1" spans="1:8">
       <c r="A26" s="6"/>
-      <c r="B26" s="16"/>
-      <c r="C26" s="17"/>
-      <c r="D26" s="11" t="s">
-        <v>65</v>
-      </c>
-      <c r="E26" s="11"/>
+      <c r="B26" s="14"/>
+      <c r="C26" s="15"/>
+      <c r="D26" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="E26" s="8"/>
       <c r="F26" s="6"/>
-      <c r="G26" s="11" t="s">
-        <v>66</v>
+      <c r="G26" s="8" t="s">
+        <v>70</v>
       </c>
       <c r="H26" s="6"/>
     </row>
     <row r="27" ht="35" customHeight="1" spans="1:8">
       <c r="A27" s="7"/>
-      <c r="B27" s="18"/>
-      <c r="C27" s="19"/>
-      <c r="D27" s="11" t="s">
-        <v>67</v>
-      </c>
-      <c r="E27" s="11"/>
+      <c r="B27" s="16"/>
+      <c r="C27" s="17"/>
+      <c r="D27" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="E27" s="8"/>
       <c r="F27" s="7"/>
-      <c r="G27" s="11" t="s">
-        <v>68</v>
+      <c r="G27" s="8" t="s">
+        <v>72</v>
       </c>
       <c r="H27" s="7"/>
     </row>
